--- a/naver-place-crawler/results_health/동작_PT.xlsx
+++ b/naver-place-crawler/results_health/동작_PT.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/again_gym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,20 +596,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5im9o</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -718,10 +722,10 @@
         <v>176</v>
       </c>
       <c r="Q3" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R3" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -774,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/upto_daebang/223764896097</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,20 +788,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/ww2t0wi</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -888,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wb85bpo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -962,7 +974,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlrja8903</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,20 +984,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4q09b</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>

--- a/naver-place-crawler/results_health/동작_PT.xlsx
+++ b/naver-place-crawler/results_health/동작_PT.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/again_gym1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,42 +596,38 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5im9o</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P2" t="n">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="Q2" t="n">
         <v>578</v>
       </c>
       <c r="R2" t="n">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -744,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -778,7 +774,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/upto_daebang/223764896097</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,24 +784,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/ww2t0wi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -842,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -896,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wb85bpo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -918,10 +906,10 @@
         <v>49</v>
       </c>
       <c r="Q5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R5" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -974,7 +962,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rlrja8903</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,24 +972,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4q09b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1038,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/동작_PT.xlsx
+++ b/naver-place-crawler/results_health/동작_PT.xlsx
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q3" t="n">
         <v>149</v>
       </c>
       <c r="R3" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>266</v>
       </c>
       <c r="Q6" t="n">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="R6" t="n">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/동작_PT.xlsx
+++ b/naver-place-crawler/results_health/동작_PT.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/again_gym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,20 +596,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5im9o</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>모브 크로스핏 / 하이록스</t>
+          <t>업투프리미엄대방역 사우나 휘트니스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>psj7091@naver.com</t>
+          <t>upto_daebang@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1316-4619</t>
+          <t>02-813-1101</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 동작구 등용로 124 B1</t>
+          <t>서울특별시 동작구 여의대방로44길 10 상가동 지하2층 상가지하 2-1호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/psj7091</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,38 +694,42 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/ww2t0wi</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="P3" t="n">
-        <v>177</v>
+        <v>1780</v>
       </c>
       <c r="Q3" t="n">
-        <v>149</v>
+        <v>322</v>
       </c>
       <c r="R3" t="n">
-        <v>326</v>
+        <v>2102</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1263828292</t>
+          <t>1605063220</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1263828292</t>
+          <t>https://m.place.naver.com/place/1605063220</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>업투프리미엄대방역 사우나 휘트니스</t>
+          <t>모브 크로스핏 / 하이록스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>upto_daebang@naver.com</t>
+          <t>psj7091@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02-813-1101</t>
+          <t>0507-1316-4619</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 동작구 여의대방로44길 10 상가동 지하2층 상가지하 2-1호</t>
+          <t>서울특별시 동작구 등용로 124 B1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/upto_daebang/223764896097</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,38 +792,42 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w8cdfde</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1780</v>
+        <v>177</v>
       </c>
       <c r="Q4" t="n">
-        <v>321</v>
+        <v>149</v>
       </c>
       <c r="R4" t="n">
-        <v>2101</v>
+        <v>326</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1605063220</t>
+          <t>1263828292</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1605063220</t>
+          <t>https://m.place.naver.com/place/1263828292</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wb85bpo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -962,7 +978,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlrja8903</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,20 +988,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4q09b</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1000,10 +1020,10 @@
         <v>266</v>
       </c>
       <c r="Q6" t="n">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="R6" t="n">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/동작_PT.xlsx
+++ b/naver-place-crawler/results_health/동작_PT.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/again_gym1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,24 +596,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5im9o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -628,10 +624,10 @@
         <v>894</v>
       </c>
       <c r="Q2" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="R2" t="n">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -684,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/upto_daebang/223764896097</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +690,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/ww2t0wi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -748,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -782,7 +774,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/psj7091</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,27 +784,23 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w8cdfde</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -846,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wb85bpo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -944,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -978,7 +962,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rlrja8903</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,24 +972,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4q09b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1042,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
